--- a/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20260707.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20260707.xlsx
@@ -1063,17 +1063,17 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>中華電</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>82,481,236</t>
+          <t>66,998,023</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -1085,17 +1085,17 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>中華電</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>66,998,023</t>
+          <t>82,481,236</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -1217,17 +1217,17 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>川湖</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>24,706,816</t>
+          <t>1,194,040</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -1239,17 +1239,17 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>川湖</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>1,194,040</t>
+          <t>24,706,816</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -1283,17 +1283,17 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>42,363,274</t>
+          <t>16,515,455</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -1305,17 +1305,17 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>16,515,455</t>
+          <t>42,363,274</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -1437,17 +1437,17 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>7769</t>
+          <t>2880</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>鴻勁</t>
+          <t>華南金</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>1,235,033</t>
+          <t>199,096,505</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -1481,17 +1481,17 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>2880</t>
+          <t>7769</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>華南金</t>
+          <t>鴻勁</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>199,096,505</t>
+          <t>1,235,033</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
